--- a/outputs/Timetable.xlsx
+++ b/outputs/Timetable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="70">
   <si>
     <t>Section</t>
   </si>
@@ -40,73 +40,86 @@
     <t>Day \ Slot</t>
   </si>
   <si>
-    <t>9:00-9:55</t>
-  </si>
-  <si>
-    <t>10:00-10:55</t>
-  </si>
-  <si>
-    <t>11:00-11:55</t>
-  </si>
-  <si>
-    <t>12:00-12:55</t>
+    <t>9:00-10:00</t>
+  </si>
+  <si>
+    <t>9:00-10:30</t>
+  </si>
+  <si>
+    <t>10:45-11:45</t>
+  </si>
+  <si>
+    <t>10:45-12:15</t>
+  </si>
+  <si>
+    <t>12:30-1:30</t>
+  </si>
+  <si>
+    <t>12:30-2:00</t>
+  </si>
+  <si>
+    <t>2:15-3:15</t>
+  </si>
+  <si>
+    <t>2:15-3:45</t>
   </si>
   <si>
     <t>Lunch Break</t>
   </si>
   <si>
-    <t>2:00-2:55</t>
-  </si>
-  <si>
-    <t>3:00-3:55</t>
-  </si>
-  <si>
-    <t>4:00-4:55</t>
-  </si>
-  <si>
-    <t>5:00-5:55</t>
+    <t>5:00-6:00</t>
   </si>
   <si>
     <t>Monday</t>
   </si>
   <si>
-    <t xml:space="preserve">CS104
+    <t xml:space="preserve">CS104 (1hr)
 F02
-Room C104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS101
+Room 101</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">CS101 (1.5hr)
 F01
-Room C105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS101
+Room 101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS101 (1hr)
 F01
-Lab L106</t>
+Room 101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS101 (1.5hr)
+F01
+Lab 201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS102 (1hr)
+F04
+Room 101</t>
   </si>
   <si>
     <t>Tuesday</t>
   </si>
   <si>
-    <t xml:space="preserve">CS102
+    <t xml:space="preserve">CS102 (1.5hr)
 F04
-Room C105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS103
+Room 101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS103 (1.5hr)
 F03
-Room C105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS103
+Room 101</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS103 (1.5hr)
 F03
-Lab L105</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
-  </si>
-  <si>
-    <t/>
+Hardware Lab 101</t>
   </si>
   <si>
     <t>Thursday</t>
@@ -115,29 +128,49 @@
     <t>Friday</t>
   </si>
   <si>
-    <t xml:space="preserve">CS104
+    <t xml:space="preserve">CS104 (1hr)
 F02
-Room C105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS102
+Room 102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS102 (1.5hr)
 F04
-Room C106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS105
+Room 102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS102 (1hr)
+F04
+Room 102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS105 (1.5hr)
 F05
-Room C105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS101
+Room 101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS101 (1hr)
 F01
-Room C106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS105
+Room 102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS101 (1.5hr)
+F01
+Room 102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS105 (1hr)
 F05
-Lab L106</t>
+Room 101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS105 (1.5hr)
+F05
+Room 102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS105 (1.5hr)
+F05
+Lab 201</t>
   </si>
   <si>
     <t>Course Code</t>
@@ -167,6 +200,9 @@
     <t>F02</t>
   </si>
   <si>
+    <t>2 (2.0hr)</t>
+  </si>
+  <si>
     <t>Computers</t>
   </si>
   <si>
@@ -179,6 +215,9 @@
     <t>F01</t>
   </si>
   <si>
+    <t>8 (11.0hr)</t>
+  </si>
+  <si>
     <t>CS102</t>
   </si>
   <si>
@@ -188,6 +227,9 @@
     <t>F04</t>
   </si>
   <si>
+    <t>6 (8.0hr)</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -200,6 +242,9 @@
     <t>F03</t>
   </si>
   <si>
+    <t>3 (4.5hr)</t>
+  </si>
+  <si>
     <t>Hardware</t>
   </si>
   <si>
@@ -210,6 +255,9 @@
   </si>
   <si>
     <t>F05</t>
+  </si>
+  <si>
+    <t>4 (5.5hr)</t>
   </si>
 </sst>
 </file>
@@ -684,7 +732,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -698,7 +746,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -712,14 +760,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="10" width="18" customWidth="1"/>
+    <col min="2" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -750,166 +798,186 @@
       <c r="J1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="I2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="5"/>
-    </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="7"/>
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="B4:C4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -917,14 +985,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="10" width="18" customWidth="1"/>
+    <col min="2" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -955,166 +1023,186 @@
       <c r="J1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1134,122 +1222,122 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3">
-        <v>12</v>
+        <v>54</v>
+      </c>
+      <c r="D3" t="s">
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4">
-        <v>8</v>
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
+        <v>63</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
